--- a/Cosas que llegan de mercado/2026/Periodo 1/Nota7.xlsx
+++ b/Cosas que llegan de mercado/2026/Periodo 1/Nota7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\GitHub\Motozom\Cosas que llegan de mercado\2026\Periodo 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F9102F9-D6C3-4473-9EFB-D6282890BC19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{444D867F-6CFE-4A11-B099-C42BAED0C63B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <t>Cantidad</t>
   </si>
@@ -61,6 +61,9 @@
   </si>
   <si>
     <t>HAN LLEGADO 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLEGARON 2 AZULES </t>
   </si>
 </sst>
 </file>
@@ -1123,6 +1126,9 @@
       <c r="J66" t="s">
         <v>5</v>
       </c>
+      <c r="M66" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="67" spans="10:13" x14ac:dyDescent="0.25">
       <c r="J67" t="s">

--- a/Cosas que llegan de mercado/2026/Periodo 1/Nota7.xlsx
+++ b/Cosas que llegan de mercado/2026/Periodo 1/Nota7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\GitHub\Motozom\Cosas que llegan de mercado\2026\Periodo 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{444D867F-6CFE-4A11-B099-C42BAED0C63B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FD6AAFD-4B14-49AA-8E30-3225F8C4A3EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
   <si>
     <t>Cantidad</t>
   </si>
@@ -54,16 +54,16 @@
     <t>2 Rojo</t>
   </si>
   <si>
-    <t>SOLO AN LLEGADO 2</t>
+    <t>SI LLEGO COMPLETO</t>
   </si>
   <si>
-    <t xml:space="preserve">LLEGARON LOS 2 NEGROS </t>
+    <t>SI LLEGO TODO COMPLETO</t>
   </si>
   <si>
-    <t>HAN LLEGADO 4</t>
+    <t>SE CANCELO SOLO</t>
   </si>
   <si>
-    <t xml:space="preserve">LLEGARON 2 AZULES </t>
+    <t>SOLO ERA UNA PIEZA LA QUE SE ENCARGO</t>
   </si>
 </sst>
 </file>
@@ -725,6 +725,9 @@
         <f>J3*K3</f>
         <v>596</v>
       </c>
+      <c r="M3" t="s">
+        <v>9</v>
+      </c>
       <c r="N3">
         <f>SUM(L3:L125)</f>
         <v>5230</v>
@@ -808,43 +811,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="10:13" x14ac:dyDescent="0.25">
       <c r="J23">
         <v>2</v>
       </c>
@@ -855,122 +858,125 @@
         <f t="shared" si="0"/>
         <v>596</v>
       </c>
-    </row>
-    <row r="24" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="M23" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L24">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L25">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L31">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L32">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="10:13" x14ac:dyDescent="0.25">
       <c r="J43">
         <v>178</v>
       </c>
@@ -981,31 +987,34 @@
         <f t="shared" si="0"/>
         <v>178</v>
       </c>
-    </row>
-    <row r="44" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="M43" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L44">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="10:13" x14ac:dyDescent="0.25">
       <c r="J45" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L47">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L48">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1126,9 +1135,6 @@
       <c r="J66" t="s">
         <v>5</v>
       </c>
-      <c r="M66" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="67" spans="10:13" x14ac:dyDescent="0.25">
       <c r="J67" t="s">
@@ -1224,7 +1230,7 @@
         <v>690</v>
       </c>
       <c r="M81" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82" spans="10:13" x14ac:dyDescent="0.25">
@@ -1419,61 +1425,61 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L113">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L115">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L116">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L117">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L118">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L119">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L120">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L121">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="10:13" x14ac:dyDescent="0.25">
       <c r="J122">
         <v>2</v>
       </c>
@@ -1484,38 +1490,41 @@
         <f t="shared" si="1"/>
         <v>1022</v>
       </c>
-    </row>
-    <row r="123" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="M122" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="123" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L123">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L124">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L125">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L126">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L127">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="10:13" x14ac:dyDescent="0.25">
       <c r="L128">
         <f t="shared" si="1"/>
         <v>0</v>
